--- a/wiki/reports/daily/2026-09-28_일일보고.xlsx
+++ b/wiki/reports/daily/2026-09-28_일일보고.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,11 +75,6 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -100,7 +95,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
+        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -205,7 +200,13 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -612,7 +613,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-09-28 08:02   |   전일: 9월 23일   |   월평균 기준: 이전 작업일 17일 평균   |   9월 누적 작업일: 18일</t>
+          <t>생성: 2026-09-28 16:07   |   전일: 9월 23일   |   월평균 기준: 이전 작업일 17일 평균   |   9월 누적 작업일: 18일</t>
         </is>
       </c>
     </row>
@@ -674,25 +675,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-16</v>
+        <v>27</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-1</v>
+        <v>1.6875</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>29.1</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-29.11764705882353</v>
+        <v>13.88235294117647</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-1</v>
+        <v>0.4767676767676768</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -703,29 +704,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0</v>
+        <v>8470</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>3083</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-3083</v>
+        <v>5387</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-1</v>
+        <v>1.747324035030814</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>7433.6</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-7433.588235294118</v>
+        <v>1036.411764705882</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-1</v>
+        <v>0.1394228106131944</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>2:21:10</t>
         </is>
       </c>
     </row>
@@ -736,25 +737,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>15</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-10</v>
+        <v>32</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-0.6666666666666666</v>
+        <v>2.133333333333333</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>18.1</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-13.05882352941176</v>
+        <v>28.94117647058824</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-0.7231270358306189</v>
+        <v>1.602605863192182</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
@@ -765,29 +766,29 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1310</v>
+        <v>9852</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>3930</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-2620</v>
+        <v>5922</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.6666666666666666</v>
+        <v>1.506870229007634</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>6926.6</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-5616.64705882353</v>
+        <v>2925.35294117647</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-0.810875306786239</v>
+        <v>0.4223331889633384</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>0:21:50</t>
+          <t>2:44:12</t>
         </is>
       </c>
     </row>
@@ -798,25 +799,25 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>31</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-26</v>
+        <v>59</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.8387096774193549</v>
+        <v>1.903225806451613</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>47.2</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-42.1764705882353</v>
+        <v>42.8235294117647</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-0.8940149625935162</v>
+        <v>0.9077306733167081</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
@@ -827,29 +828,29 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1310</v>
+        <v>18322</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>7013</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-5703</v>
+        <v>11309</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.8132040496221303</v>
+        <v>1.612576643376586</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>14360.2</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-13050.23529411765</v>
+        <v>3961.764705882353</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-0.9087758680015074</v>
+        <v>0.2758843866231915</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>0:21:50</t>
+          <t>5:05:22</t>
         </is>
       </c>
     </row>
@@ -860,25 +861,25 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>31</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-26</v>
+        <v>59</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.8387096774193549</v>
+        <v>1.903225806451613</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>46.4</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-41.41176470588236</v>
+        <v>43.58823529411764</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-0.8922686945500634</v>
+        <v>0.9391634980988592</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
@@ -890,13 +891,13 @@
       </c>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="14" t="n">
-        <v>807</v>
+        <v>892</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>245434</v>
+        <v>262446</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>794</v>
+        <v>879</v>
       </c>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="13" t="n"/>
@@ -919,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1006,149 +1007,946 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>(해당일 작업 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr"/>
+      <c r="I4" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>2320</v>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>0:38:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>0179</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>1160</v>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>0:19:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>0118 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr"/>
+      <c r="I6" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>1120</v>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>0:18:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>0179</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>609</v>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>0:10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr"/>
+      <c r="I8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>960</v>
+      </c>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>0:16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr"/>
+      <c r="I9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>549</v>
+      </c>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>0:09:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr"/>
+      <c r="I10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>192</v>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>0:03:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>0179</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr"/>
+      <c r="I11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>170</v>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>0:02:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr"/>
+      <c r="I12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>110</v>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>0:01:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>0153_D5.1</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>1280</v>
+      </c>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>0:21:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>FAST GRIND 소계</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>8470</v>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>2:21:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>■ GX7</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K7" s="19" t="inlineStr">
+      <c r="K17" s="21" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="20" t="n">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>R0.5</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C18" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="D18" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr"/>
+      <c r="I18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>0:21:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>0121</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr"/>
-      <c r="I8" s="22" t="n">
+      <c r="H19" s="22" t="inlineStr"/>
+      <c r="I19" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="24" t="n">
+        <v>262</v>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>0:04:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>0179</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr"/>
+      <c r="I20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="24" t="n">
+        <v>498</v>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>0:08:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr"/>
+      <c r="I21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="24" t="n">
+        <v>498</v>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>0:08:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="22" t="n">
-        <v>1310</v>
-      </c>
-      <c r="K8" s="20" t="inlineStr">
-        <is>
-          <t>0:21:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>0168, 0166</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr"/>
+      <c r="I22" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" s="24" t="n">
+        <v>1560</v>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>0:26:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>0168, 0166</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr"/>
+      <c r="I23" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="24" t="n">
+        <v>780</v>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>0:13:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>0168., 0166</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr"/>
+      <c r="I24" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="24" t="n">
+        <v>846</v>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>0:14:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>0168 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr"/>
+      <c r="I25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="24" t="n">
+        <v>534</v>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>0:08:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr"/>
+      <c r="I26" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="J26" s="24" t="n">
+        <v>3560</v>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>0:59:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr"/>
+      <c r="I27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>0:00:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>GX7 소계</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>1310</v>
-      </c>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>0:21:50</t>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>9852</v>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>2:44:12</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A4:K4"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
